--- a/layouts/Warehouse_Logic.xlsx
+++ b/layouts/Warehouse_Logic.xlsx
@@ -9,6 +9,7 @@
     <sheet name="PickingLocations" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="OutboundStaging" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="InboundDocks" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="SkuCatalog" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -11100,4 +11101,940 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>sku_code</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>volumen_m3</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>peso_kg</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>clase_manejo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SKU001</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.7587</v>
+      </c>
+      <c r="C2" t="n">
+        <v>88.48999999999999</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>extra_grande</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SKU002</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.6884</v>
+      </c>
+      <c r="C3" t="n">
+        <v>78.19</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>extra_grande</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SKU003</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.6596</v>
+      </c>
+      <c r="C4" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>extra_grande</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SKU004</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.08989999999999999</v>
+      </c>
+      <c r="C5" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>pesado</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SKU005</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.06850000000000001</v>
+      </c>
+      <c r="C6" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>pesado</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SKU006</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.0572</v>
+      </c>
+      <c r="C7" t="n">
+        <v>31.36</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>pesado</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SKU007</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.0415</v>
+      </c>
+      <c r="C8" t="n">
+        <v>40.42</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>pesado</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SKU008</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0354</v>
+      </c>
+      <c r="C9" t="n">
+        <v>24.32</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>pesado</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SKU009</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.0312</v>
+      </c>
+      <c r="C10" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>pesado</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SKU010</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.2138</v>
+      </c>
+      <c r="C11" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>voluminoso</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SKU011</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.2072</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>voluminoso</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SKU012</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.1794</v>
+      </c>
+      <c r="C13" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>voluminoso</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SKU013</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.1345</v>
+      </c>
+      <c r="C14" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>voluminoso</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SKU014</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.2068</v>
+      </c>
+      <c r="C15" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>voluminoso</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SKU015</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.1978</v>
+      </c>
+      <c r="C16" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>voluminoso</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SKU016</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.2344</v>
+      </c>
+      <c r="C17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>voluminoso</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SKU017</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="C18" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>voluminoso</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SKU018</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.0143</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>mediano</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SKU019</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.0384</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>mediano</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SKU020</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.0158</v>
+      </c>
+      <c r="C21" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>mediano</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SKU021</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.0274</v>
+      </c>
+      <c r="C22" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>mediano</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SKU022</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.0364</v>
+      </c>
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>mediano</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SKU023</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.0207</v>
+      </c>
+      <c r="C24" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>mediano</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SKU024</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="C25" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>mediano</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SKU025</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.0129</v>
+      </c>
+      <c r="C26" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>mediano</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SKU026</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.0311</v>
+      </c>
+      <c r="C27" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>mediano</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SKU027</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.0353</v>
+      </c>
+      <c r="C28" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>mediano</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SKU028</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>mediano</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SKU029</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.0259</v>
+      </c>
+      <c r="C30" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>mediano</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SKU030</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.0121</v>
+      </c>
+      <c r="C31" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>mediano</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SKU031</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.0252</v>
+      </c>
+      <c r="C32" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>mediano</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SKU032</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>mediano</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SKU033</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>pequeno</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SKU034</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>pequeno</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SKU035</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>pequeno</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SKU036</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>pequeno</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SKU037</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>pequeno</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SKU038</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>pequeno</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SKU039</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>pequeno</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SKU040</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0.0038</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>pequeno</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SKU041</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0.0066</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>pequeno</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SKU042</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>pequeno</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SKU043</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>pequeno</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SKU044</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>pequeno</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SKU045</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>pequeno</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SKU046</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>pequeno</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SKU047</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>pequeno</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SKU048</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>pequeno</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SKU049</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>pequeno</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SKU050</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>pequeno</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>